--- a/july 2026/LMT_JULY_26/July Orders/Risan Askari 11.xlsx
+++ b/july 2026/LMT_JULY_26/July Orders/Risan Askari 11.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDF8E11-0B06-4F17-860A-BF56279261FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91412DC2-023E-45CA-A744-1370FB00C5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3342,7 +3342,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3370,7 +3370,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4561,7 +4561,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4589,7 +4589,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5780,7 +5780,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5808,7 +5808,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -6999,7 +6999,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7027,7 +7027,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8218,7 +8218,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8246,7 +8246,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9437,7 +9437,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9465,7 +9465,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10653,7 +10653,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10681,7 +10681,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11868,7 +11868,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11896,7 +11896,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13083,7 +13083,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13111,7 +13111,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14298,7 +14298,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14326,7 +14326,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18263,7 +18263,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18291,7 +18291,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19478,7 +19478,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19506,7 +19506,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20693,7 +20693,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20721,7 +20721,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21908,7 +21908,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21936,7 +21936,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23128,7 +23128,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23156,7 +23156,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>21162.6760455</v>
+        <v>18319.931437499999</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23741,11 +23741,11 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>8716.7999999999993</v>
+        <v>5811.2</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
@@ -23753,27 +23753,27 @@
       </c>
       <c r="K20" s="171">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>305.08800000000002</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>1220.3520000000001</v>
+        <v>813.5680000000001</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>7191.36</v>
+        <v>4794.24</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1294.4448</v>
+        <v>862.96319999999992</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>42.429023999999998</v>
+        <v>28.286016</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>8528.233823999999</v>
+        <v>5685.4892159999999</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24071,7 +24071,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24082,11 +24082,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>21630.6</v>
+        <v>18725</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24094,27 +24094,27 @@
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
-        <v>757.07100000000014</v>
+        <v>655.37500000000011</v>
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>3028.2840000000006</v>
+        <v>2621.5000000000005</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>17845.245000000003</v>
+        <v>15448.125</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>3212.1441000000004</v>
+        <v>2780.6624999999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>105.2869455</v>
+        <v>91.143937500000007</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>21162.676045499997</v>
+        <v>18319.931437500003</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24244,7 +24244,7 @@
       </c>
       <c r="U30" s="164">
         <f>SUM(U14:U28)</f>
-        <v>21162.6760455</v>
+        <v>18319.931437499999</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24277,7 +24277,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="151">
         <f>I25</f>
-        <v>21630.6</v>
+        <v>18725</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24298,7 +24298,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="152">
         <f>L25</f>
-        <v>3028.2840000000006</v>
+        <v>2621.5000000000005</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24319,7 +24319,7 @@
       <c r="O34" s="240"/>
       <c r="P34" s="153">
         <f>K25</f>
-        <v>757.07100000000014</v>
+        <v>655.37500000000011</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24341,7 +24341,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="152">
         <f>P32-P33-P34</f>
-        <v>17845.244999999999</v>
+        <v>15448.125</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="P36" s="152">
         <f>N25</f>
-        <v>3212.1441000000004</v>
+        <v>2780.6624999999999</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24388,7 +24388,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="152">
         <f>P35+P36</f>
-        <v>21057.3891</v>
+        <v>18228.787499999999</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24413,7 +24413,7 @@
       </c>
       <c r="P38" s="152">
         <f>O38*P37</f>
-        <v>526.43472750000001</v>
+        <v>455.71968749999996</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24423,7 +24423,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="159">
         <f>P37+P38</f>
-        <v>21583.8238275</v>
+        <v>18684.507187499999</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24595,7 +24595,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24623,7 +24623,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25156,36 +25156,39 @@
       </c>
       <c r="G20" s="113"/>
       <c r="H20" s="114">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I20" s="115">
         <f t="shared" si="3"/>
-        <v>8716.7999999999993</v>
+        <v>5811.2</v>
       </c>
       <c r="J20" s="116"/>
       <c r="K20" s="103">
         <f t="shared" si="4"/>
-        <v>305.08800000000002</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L20" s="104">
         <f t="shared" si="5"/>
-        <v>1220.3520000000001</v>
+        <v>813.5680000000001</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="6"/>
-        <v>7191.36</v>
+        <v>4794.24</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>1294.4448</v>
+        <v>862.96319999999992</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>42.429023999999998</v>
+        <v>28.286016</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>8528.233823999999</v>
+        <v>5685.4892159999999</v>
+      </c>
+      <c r="Q20">
+        <v>-40</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25429,36 +25432,36 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>21630.6</v>
+        <v>18725</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
         <f t="shared" si="9"/>
-        <v>757.07100000000014</v>
+        <v>655.37500000000011</v>
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>3028.2840000000006</v>
+        <v>2621.5000000000005</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>17845.245000000003</v>
+        <v>15448.125</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>3212.1441000000004</v>
+        <v>2780.6624999999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>105.2869455</v>
+        <v>91.143937500000007</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>21162.676045499997</v>
+        <v>18319.931437500003</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25508,7 +25511,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>21630.6</v>
+        <v>18725</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25529,7 +25532,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>3028.2840000000006</v>
+        <v>2621.5000000000005</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25550,7 +25553,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>757.07100000000014</v>
+        <v>655.37500000000011</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25572,7 +25575,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>17845.244999999999</v>
+        <v>15448.125</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25597,7 +25600,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>3212.1441000000004</v>
+        <v>2780.6624999999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25619,7 +25622,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>21057.3891</v>
+        <v>18228.787499999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25644,7 +25647,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>105.2869455</v>
+        <v>91.143937499999993</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25654,7 +25657,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>21162.6760455</v>
+        <v>18319.931437499999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25826,7 +25829,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25854,7 +25857,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27045,7 +27048,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27073,7 +27076,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28263,7 +28266,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28291,7 +28294,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29482,7 +29485,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29510,7 +29513,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30701,7 +30704,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30729,7 +30732,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
